--- a/artfynd/A 13579-2026 artfynd.xlsx
+++ b/artfynd/A 13579-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97132928</v>
+        <v>97132942</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>101897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ältebo, Ängsbo, Gstr</t>
+          <t>Ältebo, NV gården Ängsbo, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583738</v>
+        <v>583692</v>
       </c>
       <c r="R2" t="n">
-        <v>6711445</v>
+        <v>6711450</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skog, olikåldrig, sluten, delvis grov granskog i brant,  storblockig, sydostsluttning</t>
+          <t>Skog, surdråg i anslutning till bäck omgiven av sluten blockgranskog</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 234728L</t>
+          <t>Gst Fyndnr 234719L</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -779,6 +779,117 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>97132928</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ältebo, Ängsbo, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>583738</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6711445</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2001-09-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2001-09-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skog, olikåldrig, sluten, delvis grov granskog i brant,  storblockig, sydostsluttning</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 234728L</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gunni Hedkvist</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
         </is>

--- a/artfynd/A 13579-2026 artfynd.xlsx
+++ b/artfynd/A 13579-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97132942</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97132928</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>